--- a/data/GreenCover/greenCover.xlsx
+++ b/data/GreenCover/greenCover.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Walsh\DATA ANALYTICS CAPSTONE\Project\Dataset\GreenCover\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58C5DF76-FB3A-46D0-966E-01C079539A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7500A68-6307-48F4-AD12-D52FB61364DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>City</t>
   </si>
@@ -129,6 +129,9 @@
   </si>
   <si>
     <t>Visakhapatnam</t>
+  </si>
+  <si>
+    <t>Cuttack</t>
   </si>
 </sst>
 </file>
@@ -455,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.33203125" customWidth="1"/>
@@ -536,113 +539,121 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>564.58000000000004</v>
+        <v>24</v>
+      </c>
+      <c r="B10" s="1">
+        <v>818.29</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11">
-        <v>0.93</v>
+        <v>564.58000000000004</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="1">
-        <v>1882.06</v>
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>0.93</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>47.57</v>
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1882.06</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="1">
-        <v>1043.06</v>
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>47.57</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>1112.1199999999999</v>
+        <v>1043.06</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16">
-        <v>15.97</v>
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
+        <v>1112.1199999999999</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="1">
-        <v>1716.95</v>
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>15.97</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18">
-        <v>60.07</v>
+        <v>17</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1716.95</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="1">
-        <v>2713.63</v>
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>60.07</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>1490.52</v>
+        <v>2713.63</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1">
-        <v>1754.5</v>
+        <v>1490.52</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22">
-        <v>495.86</v>
+        <v>21</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1754.5</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>495.86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>23</v>
       </c>
-      <c r="B23">
+      <c r="B24">
         <v>272.45</v>
       </c>
     </row>
